--- a/public/templates/ExportTemplate.xlsx
+++ b/public/templates/ExportTemplate.xlsx
@@ -33,7 +33,7 @@
     <t>TÊN KHÁCH HÀNG: .</t>
   </si>
   <si>
-    <t>24/06/2025 10:44:57</t>
+    <t>17/07/2025 15:43:54</t>
   </si>
   <si>
     <t xml:space="preserve">GIAO HÀNG TẠI KHO:  </t>
@@ -42,10 +42,10 @@
     <t>XUẤT TẠI KHO : CTY CP THÁI BÌNH DƯƠNG XANH</t>
   </si>
   <si>
-    <t>SỐ PXK: 10/06/25-41</t>
-  </si>
-  <si>
-    <t>SỐ XE: 62C-011.27</t>
+    <t>SỐ PXK: 08/07/25-3</t>
+  </si>
+  <si>
+    <t>SỐ XE: 62H-014.07</t>
   </si>
   <si>
     <t xml:space="preserve">STT </t>
@@ -332,24 +332,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="24"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
       <b val="0"/>
@@ -464,6 +446,24 @@
       <i val="0"/>
       <strike val="0"/>
       <u val="none"/>
+      <sz val="24"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="14"/>
       <color rgb="FF7030A0"/>
       <name val="Calibri Light"/>
@@ -484,7 +484,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -515,43 +515,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -610,10 +573,34 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -625,153 +612,153 @@
   </cellStyleXfs>
   <cellXfs count="53">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="49" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="22" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="22" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="7" numFmtId="22" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="22" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="9" numFmtId="49" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="9" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="12" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="22" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="9" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="13" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="14" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="49" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="7" numFmtId="22" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="7" numFmtId="22" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="8" numFmtId="22" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="9" numFmtId="22" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="9" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="7" numFmtId="22" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="11" numFmtId="49" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="12" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="13" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="14" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="15" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="15" numFmtId="164" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="15" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="15" numFmtId="3" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="15" numFmtId="0" fillId="0" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="15" numFmtId="1" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="15" numFmtId="164" fillId="0" borderId="11" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="15" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="15" numFmtId="0" fillId="0" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="15" numFmtId="3" fillId="0" borderId="11" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="15" numFmtId="1" fillId="0" borderId="11" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="15" numFmtId="0" fillId="2" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1111,128 +1098,128 @@
   <dimension ref="A1:AE19"/>
   <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="9.140625" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="true" style="21"/>
-    <col min="2" max="2" width="21.28515625" customWidth="true" style="22"/>
-    <col min="3" max="3" width="18.28515625" customWidth="true" style="21"/>
-    <col min="4" max="4" width="17.5703125" customWidth="true" style="23"/>
-    <col min="5" max="5" width="12.7109375" customWidth="true" style="23"/>
-    <col min="6" max="6" width="12.42578125" customWidth="true" style="23"/>
-    <col min="7" max="7" width="10.28515625" customWidth="true" style="23"/>
-    <col min="8" max="8" width="14" customWidth="true" style="23"/>
-    <col min="9" max="9" width="13" customWidth="true" style="20"/>
-    <col min="10" max="10" width="13.85546875" customWidth="true" style="20"/>
-    <col min="11" max="11" width="23" customWidth="true" style="20"/>
-    <col min="12" max="12" width="9.140625" style="26"/>
-    <col min="13" max="13" width="9.140625" style="27"/>
-    <col min="14" max="14" width="9.140625" style="27"/>
-    <col min="15" max="15" width="9.140625" style="28"/>
-    <col min="16" max="16" width="9.140625" style="28"/>
-    <col min="17" max="17" width="9.140625" style="28"/>
-    <col min="18" max="18" width="9.140625" style="28"/>
-    <col min="19" max="19" width="11.42578125" customWidth="true" style="21"/>
-    <col min="20" max="20" width="9.140625" style="21"/>
-    <col min="21" max="21" width="9.140625" style="21"/>
-    <col min="22" max="22" width="9.140625" style="21"/>
-    <col min="23" max="23" width="9.140625" style="21"/>
-    <col min="24" max="24" width="13.5703125" customWidth="true" style="21"/>
-    <col min="25" max="25" width="15.42578125" customWidth="true" style="21"/>
-    <col min="26" max="26" width="9.140625" style="21"/>
-    <col min="27" max="27" width="15" customWidth="true" style="21"/>
-    <col min="28" max="28" width="19.7109375" customWidth="true" style="21"/>
-    <col min="29" max="29" width="17.28515625" customWidth="true" style="21"/>
-    <col min="30" max="30" width="15.42578125" customWidth="true" style="21"/>
-    <col min="31" max="31" width="9.140625" style="21"/>
+    <col min="1" max="1" width="8" customWidth="true" style="18"/>
+    <col min="2" max="2" width="21.28515625" customWidth="true" style="19"/>
+    <col min="3" max="3" width="18.28515625" customWidth="true" style="18"/>
+    <col min="4" max="4" width="17.5703125" customWidth="true" style="20"/>
+    <col min="5" max="5" width="12.7109375" customWidth="true" style="20"/>
+    <col min="6" max="6" width="12.42578125" customWidth="true" style="20"/>
+    <col min="7" max="7" width="10.28515625" customWidth="true" style="20"/>
+    <col min="8" max="8" width="14" customWidth="true" style="20"/>
+    <col min="9" max="9" width="13" customWidth="true" style="17"/>
+    <col min="10" max="10" width="13.85546875" customWidth="true" style="17"/>
+    <col min="11" max="11" width="23" customWidth="true" style="17"/>
+    <col min="12" max="12" width="9.140625" style="23"/>
+    <col min="13" max="13" width="9.140625" style="24"/>
+    <col min="14" max="14" width="9.140625" style="24"/>
+    <col min="15" max="15" width="9.140625" style="25"/>
+    <col min="16" max="16" width="9.140625" style="25"/>
+    <col min="17" max="17" width="9.140625" style="25"/>
+    <col min="18" max="18" width="9.140625" style="25"/>
+    <col min="19" max="19" width="11.42578125" customWidth="true" style="18"/>
+    <col min="20" max="20" width="9.140625" style="18"/>
+    <col min="21" max="21" width="9.140625" style="18"/>
+    <col min="22" max="22" width="9.140625" style="18"/>
+    <col min="23" max="23" width="9.140625" style="18"/>
+    <col min="24" max="24" width="13.5703125" customWidth="true" style="18"/>
+    <col min="25" max="25" width="15.42578125" customWidth="true" style="18"/>
+    <col min="26" max="26" width="9.140625" style="18"/>
+    <col min="27" max="27" width="15" customWidth="true" style="18"/>
+    <col min="28" max="28" width="19.7109375" customWidth="true" style="18"/>
+    <col min="29" max="29" width="17.28515625" customWidth="true" style="18"/>
+    <col min="30" max="30" width="15.42578125" customWidth="true" style="18"/>
+    <col min="31" max="31" width="9.140625" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" customHeight="1" ht="30">
       <c r="A1"/>
       <c r="B1"/>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="42"/>
+      <c r="W1" s="42"/>
+      <c r="X1" s="42"/>
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="42"/>
+      <c r="AA1" s="42"/>
+      <c r="AB1" s="42"/>
+      <c r="AC1" s="42"/>
+      <c r="AD1" s="42"/>
       <c r="AE1"/>
     </row>
     <row r="2" spans="1:31" customHeight="1" ht="20.25">
       <c r="A2"/>
       <c r="B2"/>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43"/>
       <c r="AE2"/>
     </row>
     <row r="3" spans="1:31" customHeight="1" ht="27">
       <c r="A3"/>
       <c r="B3"/>
       <c r="C3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
       <c r="S3"/>
       <c r="T3"/>
       <c r="U3"/>
@@ -1252,25 +1239,25 @@
       <c r="B4"/>
       <c r="C4"/>
       <c r="D4"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="51" t="s">
+      <c r="E4" s="18"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="51"/>
-      <c r="P4" s="51"/>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="51"/>
-      <c r="S4" s="51"/>
-      <c r="T4" s="51"/>
-      <c r="U4" s="51"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44"/>
+      <c r="S4" s="44"/>
+      <c r="T4" s="44"/>
+      <c r="U4" s="44"/>
       <c r="V4"/>
       <c r="W4"/>
       <c r="X4"/>
@@ -1287,25 +1274,25 @@
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="52" t="s">
+      <c r="E5" s="18"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
-      <c r="P5" s="52"/>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="52"/>
-      <c r="S5" s="52"/>
-      <c r="T5" s="52"/>
-      <c r="U5" s="52"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="45"/>
+      <c r="R5" s="45"/>
+      <c r="S5" s="45"/>
+      <c r="T5" s="45"/>
+      <c r="U5" s="45"/>
       <c r="V5"/>
       <c r="W5"/>
       <c r="X5"/>
@@ -1319,28 +1306,28 @@
     </row>
     <row r="6" spans="1:31" customHeight="1" ht="27">
       <c r="A6"/>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="11" t="s">
+      <c r="E6" s="18"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="9"/>
-      <c r="S6"/>
+      <c r="Q6" s="37"/>
+      <c r="R6" s="37"/>
+      <c r="S6" s="37"/>
       <c r="T6"/>
       <c r="U6"/>
       <c r="V6"/>
@@ -1356,25 +1343,25 @@
     </row>
     <row r="7" spans="1:31" customHeight="1" ht="27">
       <c r="A7"/>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C7"/>
       <c r="D7"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
       <c r="S7"/>
       <c r="T7"/>
       <c r="U7"/>
@@ -1391,27 +1378,27 @@
     </row>
     <row r="8" spans="1:31" customHeight="1" ht="27">
       <c r="A8"/>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C8"/>
-      <c r="D8" s="13"/>
+      <c r="D8" s="10"/>
       <c r="E8"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="15" t="s">
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
       <c r="S8"/>
       <c r="T8"/>
       <c r="U8"/>
@@ -1427,27 +1414,27 @@
       <c r="AE8"/>
     </row>
     <row r="9" spans="1:31" customHeight="1" ht="27">
-      <c r="A9" s="24"/>
-      <c r="B9" s="10" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17"/>
-      <c r="S9" s="24"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="21"/>
       <c r="T9"/>
       <c r="U9"/>
       <c r="V9"/>
@@ -1463,23 +1450,23 @@
     </row>
     <row r="10" spans="1:31" customHeight="1" ht="27">
       <c r="A10"/>
-      <c r="B10" s="21"/>
+      <c r="B10" s="18"/>
       <c r="C10"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
-      <c r="P10" s="21"/>
-      <c r="Q10" s="21"/>
-      <c r="R10" s="21"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="18"/>
+      <c r="R10" s="18"/>
       <c r="S10"/>
       <c r="T10"/>
       <c r="U10"/>
@@ -1495,187 +1482,187 @@
       <c r="AE10"/>
     </row>
     <row r="11" spans="1:31" customHeight="1" ht="43.5">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="45" t="s">
+      <c r="D11" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="45" t="s">
+      <c r="E11" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="45" t="s">
+      <c r="F11" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="45" t="s">
+      <c r="G11" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="45" t="s">
+      <c r="H11" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="45" t="s">
+      <c r="I11" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="45" t="s">
+      <c r="J11" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="K11" s="45" t="s">
+      <c r="K11" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="45" t="s">
+      <c r="L11" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="M11" s="47" t="s">
+      <c r="M11" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="N11" s="45" t="s">
+      <c r="N11" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="O11" s="45" t="s">
+      <c r="O11" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="P11" s="48" t="s">
+      <c r="P11" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="Q11" s="45" t="s">
+      <c r="Q11" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="R11" s="45" t="s">
+      <c r="R11" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="S11" s="49" t="s">
+      <c r="S11" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="T11" s="45" t="s">
+      <c r="T11" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="U11" s="49" t="s">
+      <c r="U11" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="V11" s="45" t="s">
+      <c r="V11" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="W11" s="45" t="s">
+      <c r="W11" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="X11" s="50" t="s">
+      <c r="X11" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="Y11" s="45" t="s">
+      <c r="Y11" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="Z11" s="45" t="s">
+      <c r="Z11" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="AA11" s="45" t="s">
+      <c r="AA11" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="AB11" s="45" t="s">
+      <c r="AB11" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="AC11" s="46" t="s">
+      <c r="AC11" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="AD11" s="45" t="s">
+      <c r="AD11" s="47" t="s">
         <v>39</v>
       </c>
       <c r="AE11"/>
     </row>
     <row r="12" spans="1:31" customHeight="1" ht="27.75">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="H12" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="I12" s="19" t="s">
+      <c r="I12" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="19" t="s">
+      <c r="J12" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="K12" s="19" t="s">
+      <c r="K12" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="L12" s="19" t="s">
+      <c r="L12" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="M12" s="19" t="s">
+      <c r="M12" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="N12" s="19" t="s">
+      <c r="N12" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="O12" s="19" t="s">
+      <c r="O12" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="P12" s="19" t="s">
+      <c r="P12" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="Q12" s="19" t="s">
+      <c r="Q12" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="R12" s="19" t="s">
+      <c r="R12" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="S12" s="19" t="s">
+      <c r="S12" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="T12" s="19" t="s">
+      <c r="T12" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="U12" s="19" t="s">
+      <c r="U12" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="V12" s="19" t="s">
+      <c r="V12" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="W12" s="19" t="s">
+      <c r="W12" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="X12" s="19" t="s">
+      <c r="X12" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="Y12" s="19" t="s">
+      <c r="Y12" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="Z12" s="19" t="s">
+      <c r="Z12" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="AA12" s="19" t="s">
+      <c r="AA12" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="AB12" s="19" t="s">
+      <c r="AB12" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="AC12" s="19" t="s">
+      <c r="AC12" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="AD12" s="19" t="s">
+      <c r="AD12" s="16" t="s">
         <v>69</v>
       </c>
       <c r="AE12"/>
@@ -1714,15 +1701,15 @@
       <c r="AE13"/>
     </row>
     <row r="14" spans="1:31" customHeight="1" ht="48">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30" t="s">
+      <c r="A14" s="26"/>
+      <c r="B14" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32" t="s">
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36" t="s">
         <v>71</v>
       </c>
       <c r="H14" s="33"/>
@@ -1731,41 +1718,41 @@
       <c r="K14" s="33"/>
       <c r="L14" s="33"/>
       <c r="M14" s="33"/>
-      <c r="N14" s="34" t="s">
+      <c r="N14" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="O14" s="34"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="34"/>
-      <c r="S14" s="34"/>
-      <c r="T14" s="34"/>
-      <c r="U14" s="34"/>
-      <c r="V14" s="34"/>
-      <c r="W14" s="34"/>
-      <c r="X14" s="34"/>
-      <c r="Y14" s="34"/>
-      <c r="Z14" s="34"/>
-      <c r="AA14" s="34"/>
-      <c r="AB14" s="34"/>
-      <c r="AC14" s="34"/>
-      <c r="AD14" s="34"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="46"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="46"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="46"/>
+      <c r="V14" s="46"/>
+      <c r="W14" s="46"/>
+      <c r="X14" s="46"/>
+      <c r="Y14" s="46"/>
+      <c r="Z14" s="46"/>
+      <c r="AA14" s="46"/>
+      <c r="AB14" s="46"/>
+      <c r="AC14" s="46"/>
+      <c r="AD14" s="46"/>
       <c r="AE14"/>
     </row>
     <row r="15" spans="1:31" customHeight="1" ht="142.5">
       <c r="A15"/>
-      <c r="B15" s="35"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="37"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="29"/>
       <c r="N15" s="33"/>
       <c r="O15" s="33"/>
       <c r="P15" s="33"/>
@@ -1787,55 +1774,55 @@
     </row>
     <row r="16" spans="1:31" customHeight="1" ht="28.5">
       <c r="A16"/>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="44" t="s">
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="O16" s="44"/>
-      <c r="P16" s="44"/>
-      <c r="Q16" s="44"/>
-      <c r="R16" s="44"/>
-      <c r="S16" s="44"/>
-      <c r="T16" s="44"/>
-      <c r="U16" s="44"/>
-      <c r="V16" s="44"/>
-      <c r="W16" s="44"/>
-      <c r="X16" s="44"/>
-      <c r="Y16" s="44"/>
-      <c r="Z16" s="44"/>
-      <c r="AA16" s="44"/>
-      <c r="AB16" s="44"/>
-      <c r="AC16" s="44"/>
-      <c r="AD16" s="44"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="38"/>
+      <c r="U16" s="38"/>
+      <c r="V16" s="38"/>
+      <c r="W16" s="38"/>
+      <c r="X16" s="38"/>
+      <c r="Y16" s="38"/>
+      <c r="Z16" s="38"/>
+      <c r="AA16" s="38"/>
+      <c r="AB16" s="38"/>
+      <c r="AC16" s="38"/>
+      <c r="AD16" s="38"/>
       <c r="AE16"/>
     </row>
     <row r="17" spans="1:31" customHeight="1" ht="27.75">
       <c r="A17"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="37"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="29"/>
       <c r="N17" s="33"/>
       <c r="O17" s="33"/>
       <c r="P17" s="33"/>
@@ -1857,18 +1844,18 @@
     </row>
     <row r="18" spans="1:31" customHeight="1" ht="142.5">
       <c r="A18"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="43"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="32"/>
       <c r="N18" s="33"/>
       <c r="O18" s="33"/>
       <c r="P18" s="33"/>
@@ -1928,16 +1915,16 @@
     <mergeCell ref="I4:U4"/>
     <mergeCell ref="I5:U5"/>
     <mergeCell ref="N14:AD14"/>
+    <mergeCell ref="B17:M18"/>
+    <mergeCell ref="N17:AD18"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="G14:M14"/>
+    <mergeCell ref="P6:S6"/>
     <mergeCell ref="N15:AD15"/>
     <mergeCell ref="N16:AD16"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="G15:M15"/>
     <mergeCell ref="B16:M16"/>
-    <mergeCell ref="B17:M18"/>
-    <mergeCell ref="N17:AD18"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="G14:M14"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
